--- a/templates/office/EMP_MAN_060_변경관리대장.xlsx
+++ b/templates/office/EMP_MAN_060_변경관리대장.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 AI 기반 화장품 표시광고 심의 및 리스크 예방 시스템 구축</t>
+          <t>한빛글로벌 엔터프라이즈 AI 콘텐츠·규제 심의 자동화 시스템(SyncGuard AI) 구축</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>(주)아모레퍼시픽 (HANBIT GLOBAL)</t>
+          <t>㈜한빛글로벌 (Hanbit Global Corp.)</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>㈜그로브소프트 (EMPASY)</t>
+          <t>㈜엠파시 (Empasy Inc.)</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 RA / PM</t>
+          <t>한빛글로벌 RA / PM</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 기술PM / RA</t>
+          <t>한빛글로벌 기술PM / RA</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>티움넷(심의 의뢰·뷰어 링크·결과 회신) 및 마이비커(전성분·배합한도·인체적용시험 실증) 상세 연계 구체화</t>
+          <t>마케팅허브(심의 의뢰·뷰어 링크·결과 회신) 및 프로덕트랩(전성분·배합한도·인체적용시험 실증) 상세 연계 구체화</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 기술PM</t>
+          <t>한빛글로벌 기술PM</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 착수킥오프</t>
+          <t>한빛글로벌 착수킥오프</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">

--- a/templates/office/EMP_MAN_060_변경관리대장.xlsx
+++ b/templates/office/EMP_MAN_060_변경관리대장.xlsx
@@ -529,7 +529,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SyncGuard AI 프로젝트 요구사항 및 설계 변경 요청(Change Request) 승인·반영 이력</t>
+          <t>SyncFlow AI 프로젝트 요구사항 및 설계 변경 요청(Change Request) 승인·반영 이력</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>한빛글로벌 엔터프라이즈 AI 콘텐츠·규제 심의 자동화 시스템(SyncGuard AI) 구축</t>
+          <t>한빛글로벌 지능형 공급망 구매·조달 계약 및 부품 품질규격 AI 검증 플랫폼(SyncFlow AI) 구축</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>CCB 심의 결과</t>
+          <t>CCB 검증 결과</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>한빛글로벌 RA / PM</t>
+          <t>한빛글로벌 QA / PM</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>동영상(MP4) 재생 중 사용자가 심의할 여러 장면을 직접 지정하여 이미지(스냅샷)로 캡처·저장한 후 일괄 AI 심의 수행 방식 도입</t>
+          <t>설계도면(CAD/PDF) 재생 중 사용자가 검증할 여러 장면을 직접 지정하여 이미지(스냅샷)로 스냅샷·저장한 후 일괄 AI 검증 수행 방식 도입</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>한빛글로벌 기술PM / RA</t>
+          <t>한빛글로벌 기술PM / QA</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>마케팅허브(심의 의뢰·뷰어 링크·결과 회신) 및 프로덕트랩(전성분·배합한도·인체적용시험 실증) 상세 연계 구체화</t>
+          <t>전자구매포털(검증 요청·뷰어 링크·결과 회신) 및 피엘엠넥서스(자재BOM·유해물질한도·공인신뢰성시험 시험검증) 상세 연계 구체화</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>KT 레몬 연계를 필수에서 [Option / 선택사양]으로 변경 (상용 LLM 직접 파싱 대비 정확도 비교 테스트 후 최종 결정)</t>
+          <t>HB-Monitor 연계를 필수에서 [Option / 선택사양]으로 변경 (상용 LLM 직접 파싱 대비 정확도 비교 테스트 후 최종 결정)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>국·영문 혼용 문구 번역 심의는 과업 범위에 포함하고, 인물 얼굴/딥페이크 판별 및 해외 법률 심의는 과업 제외로 경계 확정</t>
+          <t>국·영문 혼용 조항 번역 검증은 과업 범위에 포함하고, 3D 솔리드 모델링 구조 해석 및 해외 법률 검증은 과업 제외로 경계 확정</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
